--- a/data/cs_people.xlsx
+++ b/data/cs_people.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E135"/>
+  <dimension ref="A1:E169"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -257,223 +257,223 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Brian Bealer</t>
+          <t>Brian Costello</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Robotics</t>
+          <t>Coding/Robotics Club</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Auburn High School, Auburn</t>
+          <t>Atlantic Co Jdc, Egg Harbor City</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>brianbealer@aecsd.education</t>
+          <t>costellb@eht.k12.nj.us</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://www.aecsd.education/districtpage.cfm?pageid=3647</t>
+          <t>https://ehtnjathletics.com/main/otherad?contentID=55531614</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Hannah McFadden</t>
+          <t>Louis DeStefano</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Mathematics/Computer Science</t>
+          <t>Coding/Robotics Club</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bard High School Early College Queens, Long Island City</t>
+          <t>Atlantic Co Jdc, Egg Harbor City</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>hmcfadden@bhsec.bard.edu</t>
+          <t>destefal@eht.k12.nj.us</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://bhsec.bard.edu/queens/academics/division-of-mathematics-and-science/</t>
+          <t>https://ehtnjathletics.com/main/otherad?contentID=55531614</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Amy Nelson</t>
+          <t>Brian Bealer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Computer Science Club Advisor</t>
+          <t>Robotics</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Batavia High School, Batavia</t>
+          <t>Auburn High School, Auburn</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>amy.nelson@bps101.net</t>
+          <t>brianbealer@aecsd.education</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://bhs.bps101.net/activity-and-athletic-fair/</t>
+          <t>https://www.aecsd.education/districtpage.cfm?pageid=3647</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Danny Ng</t>
+          <t>Hannah McFadden</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>HighSchool Computer Science &amp; Math Teacher</t>
+          <t>Mathematics/Computer Science</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Bayonne Academy, Bayonne</t>
+          <t>Bard High School Early College Queens, Long Island City</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>teacherdng@bboed.org</t>
+          <t>hmcfadden@bhsec.bard.edu</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://sites.google.com/hcstonline.org/hcplc/mathematics</t>
+          <t>https://bhsec.bard.edu/queens/academics/division-of-mathematics-and-science/</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Leon LaSpina</t>
+          <t>Amy Nelson</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Computer Science &amp; Math Teacher</t>
+          <t>Computer Science Club Advisor</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bethpage Senior High School, Bethpage</t>
+          <t>Batavia High School, Batavia</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>llaspina@bethpageeagles.ws</t>
+          <t>amy.nelson@bps101.net</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://newyork.csteachers.org/regions/longisland</t>
+          <t>https://bhs.bps101.net/activity-and-athletic-fair/</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Brian Miller</t>
+          <t>Danny Ng</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Computer Science Club Advisor</t>
+          <t>HighSchool Computer Science &amp; Math Teacher</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bloomfield High School, Bloomfield</t>
+          <t>Bayonne Academy, Bayonne</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>bmiller@bloomfield.k12.nj.us</t>
+          <t>teacherdng@bboed.org</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://bhs.bloomfield.k12.nj.us/apps/pages/index.jsp?type=d&amp;uREC_ID=369376</t>
+          <t>https://sites.google.com/hcstonline.org/hcplc/mathematics</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Christopher Lo</t>
+          <t>Danny Ng</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Coding Café Club</t>
+          <t>High School Computer Science &amp; Math Teacher</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Briarcliff High School, Briarcliff Manor</t>
+          <t>Bayonne Alternative High School, Bayonne</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>clo@briarcliffschools.org</t>
+          <t>dng@bboed.org</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://www.briarcliffschools.org/cf_enotify/view.cfm?n=2877</t>
+          <t>https://sites.google.com/hcstonline.org/hcplc/mathematics</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Edward Burns</t>
+          <t>Patel Rm</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Computer Science Teacher</t>
+          <t>Computer Science Club Advisor</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bronx Community High School, Bronx</t>
+          <t>Bayonne High School, Bayonne</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>eburns3@schools.nyc.gov</t>
+          <t>kopatel@bboed.org</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://bxscience.edu/apps/pages/index.jsp?pREC_ID=staff&amp;termREC_ID=&amp;type=d&amp;uREC_ID=3733</t>
+          <t>https://resources.finalsite.net/images/v1759158622/bboedorg/yub7distcovgx2fsikuy/BHSSports_Clubs_Activities2025-2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Wendy Qiu</t>
+          <t>Kymberly Acu</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -483,213 +483,213 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bronx Community High School, Bronx</t>
+          <t>Bergen County Academies, Hackensack</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>wqiu@schools.nyc.gov</t>
+          <t>kymacu@bergen.org</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://bxscience.edu/apps/pages/index.jsp?pREC_ID=staff&amp;termREC_ID=&amp;type=d&amp;uREC_ID=3733</t>
+          <t>https://bca-admissions.bergen.org/pdfs/BCA_School_Profile.pdf</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Edward Burns</t>
+          <t>Leon LaSpina</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Computer Science Teacher</t>
+          <t>Computer Science &amp; Math Teacher</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bronx High School for Writing and Communication Arts, Bronx</t>
+          <t>Bethpage Senior High School, Bethpage</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>eburns3@schools.nyc.gov</t>
+          <t>llaspina@bethpageeagles.ws</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://www.bxscience.edu/apps/pages/index.jsp?hideMenu=false&amp;pREC_ID=439481&amp;type=d&amp;uREC_ID=219379</t>
+          <t>https://newyork.csteachers.org/regions/longisland</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Wendy Qiu</t>
+          <t>Brian Miller</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Computer Science Teacher</t>
+          <t>Adviser - Computer Club</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bronx High School for Writing and Communication Arts, Bronx</t>
+          <t>Bloomfield High School, Bloomfield</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>wqiu@schools.nyc.gov</t>
+          <t>bmiller@bloomfield.k12.nj.us</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://www.bxscience.edu/apps/pages/index.jsp?hideMenu=false&amp;pREC_ID=439481&amp;type=d&amp;uREC_ID=219379</t>
+          <t>https://bhs.bloomfield.k12.nj.us/apps/pages/index.jsp?type=d&amp;uREC_ID=369376</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Edward Burns</t>
+          <t>Brian Miller</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Computer Science Teacher</t>
+          <t>Computer Science Club Advisor</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bronx High School of Business, Bronx</t>
+          <t>Bloomfield High School, Bloomfield</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>eburns3@schools.nyc.gov</t>
+          <t>bmiller@bloomfield.k12.nj.us</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://www.bxscience.edu/apps/pages/index.jsp?pREC_ID=staff&amp;type=d&amp;uREC_ID=3733</t>
+          <t>https://bhs.bloomfield.k12.nj.us/apps/pages/index.jsp?type=d&amp;uREC_ID=369376</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Wendy Qiu</t>
+          <t>David Romancheck</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Computer Science Teacher</t>
+          <t>Computer Science Honor Society Advisor</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bronx High School of Business, Bronx</t>
+          <t>Bound Brook High School, Bound Brook</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>wqiu@schools.nyc.gov</t>
+          <t>dromancheck@bbrook.k12.nj.us</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://www.bxscience.edu/apps/pages/index.jsp?pREC_ID=staff&amp;type=d&amp;uREC_ID=3733</t>
+          <t>https://sites.google.com/view/romancheck/home</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Edward Burns</t>
+          <t>Maureen Ryan</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Computer Science Teacher</t>
+          <t>Computer Science</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bronx High School of Science (the), Bronx</t>
+          <t>Bound Brook High School, Bound Brook</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>eburns3@schools.nyc.gov</t>
+          <t>mryan@bbrook.k12.nj.us</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://www.bxscience.edu/apps/staff/index.jsp</t>
+          <t>https://bbhs.bbrook.org/staff-directory</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Wendy Qiu</t>
+          <t>Christopher Lo</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Computer Science Teacher</t>
+          <t>Coding Café Club</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Bronx High School of Science (the), Bronx</t>
+          <t>Briarcliff High School, Briarcliff Manor</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>wqiu@schools.nyc.gov</t>
+          <t>clo@briarcliffschools.org</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://www.bxscience.edu/apps/staff/index.jsp</t>
+          <t>https://www.briarcliffschools.org/cf_enotify/view.cfm?n=2877</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rebecca Adler</t>
+          <t>Edward Burns</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Algebra and AP Computer Science</t>
+          <t>Computer Science Teacher</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Bronx Leadership Academy Ii High School, Bronx</t>
+          <t>Bronx Community High School, Bronx</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>radler9@schools.nyc.gov</t>
+          <t>eburns3@schools.nyc.gov</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://www.bla2hs.org/apps/pages/index.jsp?type=u&amp;uREC_ID=1761395</t>
+          <t>https://bxscience.edu/apps/pages/index.jsp?pREC_ID=staff&amp;termREC_ID=&amp;type=d&amp;uREC_ID=3733</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Marianne Islas</t>
+          <t>Wendy Qiu</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -699,51 +699,51 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Bronxdale High School, Bronx</t>
+          <t>Bronx Community High School, Bronx</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>mislas2@schools.nyc.gov</t>
+          <t>wqiu@schools.nyc.gov</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://www.bronxdalehs.org/apps/pages/index.jsp?pREC_ID=2519037&amp;type=u&amp;uREC_ID=2593523</t>
+          <t>https://bxscience.edu/apps/pages/index.jsp?pREC_ID=staff&amp;termREC_ID=&amp;type=d&amp;uREC_ID=3733</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Cleon Barrett</t>
+          <t>Edward Burns</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>AP Computer Science Principles Teacher</t>
+          <t>Computer Science Teacher</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Brooklyn Laboratory Charter School, Brooklyn</t>
+          <t>Bronx High School for Writing and Communication Arts, Bronx</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>c@bklabprep.org</t>
+          <t>eburns3@schools.nyc.gov</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://www.signalhire.com/companies/brooklyn-laboratory-charter-school/employees</t>
+          <t>https://www.bxscience.edu/apps/pages/index.jsp?hideMenu=false&amp;pREC_ID=439481&amp;type=d&amp;uREC_ID=219379</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Nomie Keusch Baker</t>
+          <t>Wendy Qiu</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -753,78 +753,78 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Broome Street Academy Charter High School, New York</t>
+          <t>Bronx High School for Writing and Communication Arts, Bronx</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>h@broomestreetacademy.org</t>
+          <t>wqiu@schools.nyc.gov</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://www.signalhire.com/profiles/naomi-keusch-baker%27s-email/136607861</t>
+          <t>https://www.bxscience.edu/apps/pages/index.jsp?hideMenu=false&amp;pREC_ID=439481&amp;type=d&amp;uREC_ID=219379</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Chris Paske</t>
+          <t>Edward Burns</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>PTECH Computer Science</t>
+          <t>Computer Science Teacher</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Broome-Delaware-Tioga BOCES, Binghamton</t>
+          <t>Bronx High School of Business, Bronx</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>cpaske@btboces.prg</t>
+          <t>eburns3@schools.nyc.gov</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://www.btboces.org/PTECH.aspx</t>
+          <t>https://www.bxscience.edu/apps/pages/index.jsp?pREC_ID=staff&amp;type=d&amp;uREC_ID=3733</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Nicole Waskie-Laura</t>
+          <t>Wendy Qiu</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Computer Science and Digital Literacy</t>
+          <t>Computer Science Teacher</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Broome-Delaware-Tioga BOCES, Binghamton</t>
+          <t>Bronx High School of Business, Bronx</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>nwaskiel@btboces.org</t>
+          <t>wqiu@schools.nyc.gov</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://www.btboces.org/PLIC-ComputerScienceSmartStart.aspx</t>
+          <t>https://www.bxscience.edu/apps/pages/index.jsp?pREC_ID=staff&amp;type=d&amp;uREC_ID=3733</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Emily Montroy</t>
+          <t>Edward Burns</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -834,24 +834,24 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Brushton Grade School, Brushton</t>
+          <t>Bronx High School of Science (the), Bronx</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>emily.montroy@bmcsd.org</t>
+          <t>eburns3@schools.nyc.gov</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://www.bmcsd.org/staff?page_no=6</t>
+          <t>https://www.bxscience.edu/apps/staff/index.jsp</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Emily Montroy</t>
+          <t>Wendy Qiu</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -861,240 +861,240 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Brushton-Moira High School, Brushton</t>
+          <t>Bronx High School of Science (the), Bronx</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>emily.montroy@bmcsd.org</t>
+          <t>wqiu@schools.nyc.gov</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://www.bmcsd.org/staff?page_no=6</t>
+          <t>https://www.bxscience.edu/apps/staff/index.jsp</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Quinn McFee</t>
+          <t>Rebecca Adler</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Computer Science Teacher</t>
+          <t>Algebra and AP Computer Science</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Central Park East High School, New York</t>
+          <t>Bronx Leadership Academy Ii High School, Bronx</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>qmcfee@schools.nyc.gov</t>
+          <t>radler9@schools.nyc.gov</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://www.centralparkeasths.org/copy-of-staff-directory-1</t>
+          <t>https://www.bla2hs.org/apps/pages/index.jsp?type=u&amp;uREC_ID=1761395</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Elizabeth Pegarella</t>
+          <t>Marianne Islas</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>H/S Math/Computer Science</t>
+          <t>Computer Science Teacher</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Chatham High School, Chatham</t>
+          <t>Bronxdale High School, Bronx</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>wheatm@chatham.k12.ny.us</t>
+          <t>mislas2@schools.nyc.gov</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://www.chathamcentralschools.com/o/chs/page/teacher-pages</t>
+          <t>https://www.bronxdalehs.org/apps/pages/index.jsp?pREC_ID=2519037&amp;type=u&amp;uREC_ID=2593523</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Kelly Bosco</t>
+          <t>Cleon Barrett</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Computer Science Club Advisor</t>
+          <t>AP Computer Science Principles Teacher</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Churchville-Chili Senior High School, Churchville</t>
+          <t>Brooklyn Laboratory Charter School, Brooklyn</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>kbosco@cccsd.org</t>
+          <t>c@bklabprep.org</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://www.cccsd.org/programs/fine-arts/fine-arts-clubs</t>
+          <t>https://www.signalhire.com/companies/brooklyn-laboratory-charter-school/employees</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Jeff Welton</t>
+          <t>Nomie Keusch Baker</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Computer Science Club Advisor</t>
+          <t>Computer Science Teacher</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>City Honors School, Buffalo</t>
+          <t>Broome Street Academy Charter High School, New York</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>jswelton@buffaloschools.org</t>
+          <t>h@broomestreetacademy.org</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://cityhonors.org/school-life/clubs-and-activities/</t>
+          <t>https://www.signalhire.com/profiles/naomi-keusch-baker%27s-email/136607861</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Abigaile Kimbrell</t>
+          <t>Chris Paske</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Robotics Club Advisor</t>
+          <t>PTECH Computer Science</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Clarkstown South Senior High School, West Nyack</t>
+          <t>Broome-Delaware-Tioga BOCES, Binghamton</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>akimbrell@ccsd.edu</t>
+          <t>cpaske@btboces.prg</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://south.ccsd.edu/students/activities-and-clubs/robotics-club</t>
+          <t>https://www.btboces.org/PTECH.aspx</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Morgan Milleisen</t>
+          <t>Nicole Waskie-Laura</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Robotics Engineering</t>
+          <t>Computer Science and Digital Literacy</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Cold Spring Harbor High School, Cold Spring Harbor</t>
+          <t>Broome-Delaware-Tioga BOCES, Binghamton</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>mmilleisen@csh.k12.ny.us</t>
+          <t>nwaskiel@btboces.org</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://www.csh.k12.ny.us/departments/curriculum-and-instruction-k-12/science/technology-education</t>
+          <t>https://www.btboces.org/PLIC-ComputerScienceSmartStart.aspx</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>nate levenseller</t>
+          <t>Emily Montroy</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Essentials of Computer Science, AP Computer Science(Principles and A), and Video Game Design</t>
+          <t>Computer Science Teacher</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Curtis High School, Staten Island</t>
+          <t>Brushton Grade School, Brushton</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>nlevenseller@upsd83.org</t>
+          <t>emily.montroy@bmcsd.org</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://sites.google.com/upsd83.org/chscte/teacher-pages</t>
+          <t>https://www.bmcsd.org/staff?page_no=6</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Tracie Mezera-juarez</t>
+          <t>Emily Montroy</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Essentials of Computer Science</t>
+          <t>Computer Science Teacher</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Curtis High School, Staten Island</t>
+          <t>Brushton-Moira High School, Brushton</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>tmezera-juarez@upsd83.org</t>
+          <t>emily.montroy@bmcsd.org</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://sites.google.com/upsd83.org/chscte/teacher-pages</t>
+          <t>https://www.bmcsd.org/staff?page_no=6</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Brianne Hertzog</t>
+          <t>Quinn McFee</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1104,321 +1104,321 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Deer Park High School, Deer Park</t>
+          <t>Central Park East High School, New York</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>hertzog.b@deerparkschools.org</t>
+          <t>qmcfee@schools.nyc.gov</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://deerparkschools.org/hs_departments/technology_dept</t>
+          <t>https://www.centralparkeasths.org/copy-of-staff-directory-1</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Ryan Krause</t>
+          <t>Elizabeth Pegarella</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Musical Theater/ Computer Science</t>
+          <t>H/S Math/Computer Science</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Dr Susan S McKinney Secondary School of the Arts, Brooklyn</t>
+          <t>Chatham High School, Chatham</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>rkrause@mckinneyssa.com</t>
+          <t>wheatm@chatham.k12.ny.us</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://www.mckinneyssa.com/about/faculty-staff</t>
+          <t>https://www.chathamcentralschools.com/o/chs/page/teacher-pages</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Allison Peet</t>
+          <t>Kelly Bosco</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Computer Science courses</t>
+          <t>Computer Science Club Advisor</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Dryden High School, Dryden</t>
+          <t>Churchville-Chili Senior High School, Churchville</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>apeet1@dryden.k12.ny.us</t>
+          <t>kbosco@cccsd.org</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://www.nysed.gov/edtech/learning-technology-grant-program-overview-2021-2024-dryden-central-schools-consortium</t>
+          <t>https://www.cccsd.org/programs/fine-arts/fine-arts-clubs</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Michael Gauthier</t>
+          <t>Jeff Welton</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Robotics Club Advisor</t>
+          <t>Computer Science Club Advisor</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Duanesburg High School, Delanson</t>
+          <t>City Honors School, Buffalo</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>book@duanesburg.org</t>
+          <t>jswelton@buffaloschools.org</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://www.duanesburg.org/jr-sr-high-school/arts-and-activities/</t>
+          <t>https://cityhonors.org/school-life/clubs-and-activities/</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Faiyan Talukder</t>
+          <t>Abigaile Kimbrell</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Computer Science &amp; Physics</t>
+          <t>Robotics Club Advisor</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>East New York Arts and Civics High School (the), Brooklyn</t>
+          <t>Clarkstown South Senior High School, West Nyack</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>ftalukder2@schools.nyc.gov</t>
+          <t>akimbrell@ccsd.edu</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://www.teachhs.org/staff-directory</t>
+          <t>https://south.ccsd.edu/students/activities-and-clubs/robotics-club</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Alicia Wade</t>
+          <t>Morgan Milleisen</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Teacher Computer Science/Technology</t>
+          <t>Robotics Engineering</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>East Williamsburg Scholars Academy, Brooklyn</t>
+          <t>Cold Spring Harbor High School, Cold Spring Harbor</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>awade5@schools.nyc.gov</t>
+          <t>mmilleisen@csh.k12.ny.us</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://www.ew-sa.org/science</t>
+          <t>https://www.csh.k12.ny.us/departments/curriculum-and-instruction-k-12/science/technology-education</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Cheryl Voelker</t>
+          <t>Jennifer Laderia</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>COMPUTER SCIENCE</t>
+          <t>Computer Science Teacher</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>El Puente Academy for Peace and Justice, Brooklyn</t>
+          <t>College Achieve Paterson Charter School, Paterson</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>cvoelker2@schools.nyc.gov</t>
+          <t>jladeria@collegeachieve.org</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://img1.wsimg.com/blobby/go/36743b8c-e63e-4b88-aae9-2abcfea4f55f/TO%20Part%20II.pdf</t>
+          <t>https://collegeachievepaterson.org/who-we-are/our-team/</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Maria Graziosi</t>
+          <t>nate levenseller</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>AP COMPUTER SCIENCE</t>
+          <t>Essentials of Computer Science, AP Computer Science(Principles and A), and Video Game Design</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Facing History School (the), New York</t>
+          <t>Curtis High School, Staten Island</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>croberts16@schools.nyc.gov</t>
+          <t>nlevenseller@upsd83.org</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://facinghistoryschool.org/staff-directory/</t>
+          <t>https://sites.google.com/upsd83.org/chscte/teacher-pages</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Cheryl Voelker</t>
+          <t>Tracie Mezera-juarez</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>COMPUTER SCIENCE</t>
+          <t>Essentials of Computer Science</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Fdny-Captain Vernon A Richards HS, Brooklyn</t>
+          <t>Curtis High School, Staten Island</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>cvoelker2@schools.nyc.gov</t>
+          <t>tmezera-juarez@upsd83.org</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://img1.wsimg.com/blobby/go/36743b8c-e63e-4b88-aae9-2abcfea4f55f/TO%20Part%20II.pdf</t>
+          <t>https://sites.google.com/upsd83.org/chscte/teacher-pages</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Cheryl Voelker</t>
+          <t>Brianne Hertzog</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>COMPUTER SCIENCE</t>
+          <t>Computer Science Teacher</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Frederick Douglass Academy Vii High School, Brooklyn</t>
+          <t>Deer Park High School, Deer Park</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>cvoelker2@schools.nyc.gov</t>
+          <t>hertzog.b@deerparkschools.org</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>https://img1.wsimg.com/blobby/go/36743b8c-e63e-4b88-aae9-2abcfea4f55f/TO%20Part%20II.pdf</t>
+          <t>https://deerparkschools.org/hs_departments/technology_dept</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Joseph Virgilio</t>
+          <t>Ryan Krause</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Computer Science Lead</t>
+          <t>Musical Theater/ Computer Science</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>George W Hewlett High School, Hewlett</t>
+          <t>Dr Susan S McKinney Secondary School of the Arts, Brooklyn</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>jvirgilio@hewlett-woodmere.net</t>
+          <t>rkrause@mckinneyssa.com</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://hhs.hewlett-woodmere.net/academics/listing-of-departments-by-name/business-computer-science</t>
+          <t>https://www.mckinneyssa.com/about/faculty-staff</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Meeting Time</t>
+          <t>Allison Peet</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Computer Science Teacher</t>
+          <t>Computer Science courses</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Goshen Central High School, Goshen</t>
+          <t>Dryden High School, Dryden</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>aileen.behringer@gcsny.org</t>
+          <t>apeet1@dryden.k12.ny.us</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>https://www.gcsny.org/ghs-clubs-activities</t>
+          <t>https://www.nysed.gov/edtech/learning-technology-grant-program-overview-2021-2024-dryden-central-schools-consortium</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Dillon Johnson</t>
+          <t>Michael Gauthier</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1428,294 +1428,294 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Goshen Secure Center, Goshen</t>
+          <t>Duanesburg High School, Delanson</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>dillon.johnson@gcsny.org</t>
+          <t>book@duanesburg.org</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>https://www.gcsny.org/ghs-clubs-activities</t>
+          <t>https://www.duanesburg.org/jr-sr-high-school/arts-and-activities/</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Meeting Time</t>
+          <t>Faiyan Talukder</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Computer Science Teacher</t>
+          <t>Computer Science &amp; Physics</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Goshen Secure Center, Goshen</t>
+          <t>East New York Arts and Civics High School (the), Brooklyn</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>aileen.behringer@gcsny.org</t>
+          <t>ftalukder2@schools.nyc.gov</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>https://www.gcsny.org/ghs-clubs-activities</t>
+          <t>https://www.teachhs.org/staff-directory</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Alicia Gominiak</t>
+          <t>Alicia Wade</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Computer Science/ STEM</t>
+          <t>Teacher Computer Science/Technology</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Gowanda High School, Gowanda</t>
+          <t>East Williamsburg Scholars Academy, Brooklyn</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>msgominiak@gcslearn.org</t>
+          <t>awade5@schools.nyc.gov</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>https://gowcsd.org/directory/</t>
+          <t>https://www.ew-sa.org/science</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Peter Allen-Lamphere</t>
+          <t>Cheryl Voelker</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>MATHEMATICS, AP COMPUTER SCIENCE, &amp; ROBOTICS</t>
+          <t>COMPUTER SCIENCE</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Gregorio Luperon High School for Science and Mathematics, New York</t>
+          <t>El Puente Academy for Peace and Justice, Brooklyn</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>plamphe@schools.nyc.gov</t>
+          <t>cvoelker2@schools.nyc.gov</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>https://www.glhs.nyc/staff</t>
+          <t>https://img1.wsimg.com/blobby/go/36743b8c-e63e-4b88-aae9-2abcfea4f55f/TO%20Part%20II.pdf</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Michael Piscitelli</t>
+          <t>Amir Ressaissi</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Computer Science Teacher</t>
+          <t>Robotics Advisor</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Guilderland High School, Guilderland Center</t>
+          <t>Essex Co Jdc, Newark</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>piscitellim@guilderlandschools.net</t>
+          <t>aressaissi@essextech.org</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>https://www.guilderlandschools.org/guilderland-high-school/clubs-and-activities/</t>
+          <t>https://www.essextech.org/extracurricular-activities/</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Kaci Nowadly</t>
+          <t>Amir Ressaissi</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Computer Club Advisor</t>
+          <t>Robotics Advisor</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Hamburg High School, Hamburg</t>
+          <t>Essex Rch, Newark</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>knowadly@hcsdk12.org</t>
+          <t>aressaissi@essextech.org</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>https://sites.google.com/hcsdk12.org/counselingcenter/clubs-activities-sports</t>
+          <t>https://www.essextech.org/view-entire-directory/</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Jackson Lindie</t>
+          <t>Amir Ressaissi</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Computer Science Instructor</t>
+          <t>Robotics Advisor</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Hammond Central School, Hammond</t>
+          <t>Essex Regional School, Newark</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>lkjackson@hammond.k12.in.us</t>
+          <t>aressaissi@essextech.org</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>https://campussuite-storage.s3.amazonaws.com/prod/1559033/fab8744a-ab41-11ea-9bfa-127f10bcdb1b/2674154/cabcb666-6222-11ee-80d6-0a58a9feac02/file/ACC%20Contact%20List%202023-24.pdf</t>
+          <t>https://www.essextech.org/extracurricular-activities/</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Chevonese Cornwall</t>
+          <t>Maria Graziosi</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Engineering/Computer Science Teacher</t>
+          <t>AP COMPUTER SCIENCE</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Harry S Truman High School, Bronx</t>
+          <t>Facing History School (the), New York</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>ccornwall@schools.nyc.gov</t>
+          <t>croberts16@schools.nyc.gov</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>https://www.bxtrumanhighschool.com/groups/compsci/</t>
+          <t>https://facinghistoryschool.org/staff-directory/</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Marisa Laks</t>
+          <t>Cheryl Voelker</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Computer Science Teacher/School Programmer</t>
+          <t>COMPUTER SCIENCE</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>High School for Environmental Studies, New York</t>
+          <t>Fdny-Captain Vernon A Richards HS, Brooklyn</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>laks.marisa@gmail.com</t>
+          <t>cvoelker2@schools.nyc.gov</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>https://newyork.csteachers.org/cstanewyork/regions/nyc</t>
+          <t>https://img1.wsimg.com/blobby/go/36743b8c-e63e-4b88-aae9-2abcfea4f55f/TO%20Part%20II.pdf</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Javier Trejo</t>
+          <t>Cheryl Voelker</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Computer Science Lead</t>
+          <t>COMPUTER SCIENCE</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>High School for Health Careers &amp; Sciences, New York</t>
+          <t>Frederick Douglass Academy Vii High School, Brooklyn</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>jtrejo@schools.nyc.gov</t>
+          <t>cvoelker2@schools.nyc.gov</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>https://pintel.ai/school-intel/high-school-for-health-careers-and-sciences</t>
+          <t>https://img1.wsimg.com/blobby/go/36743b8c-e63e-4b88-aae9-2abcfea4f55f/TO%20Part%20II.pdf</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Jennifer Allard</t>
+          <t>Joseph Virgilio</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Computer Science</t>
+          <t>Computer Science Lead</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Ichabod Crane Senior High School, Valatie</t>
+          <t>George W Hewlett High School, Hewlett</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>jallard@ichabodcrane.org</t>
+          <t>jvirgilio@hewlett-woodmere.net</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>https://www.ichabodcrane.org/contact/</t>
+          <t>https://hhs.hewlett-woodmere.net/academics/listing-of-departments-by-name/business-computer-science</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Additional Application Instructions</t>
+          <t>Meeting Time</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1725,638 +1725,638 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>International Leadership Charter High School, Bronx</t>
+          <t>Goshen Central High School, Goshen</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>lbeltre@ilchs.org</t>
+          <t>aileen.behringer@gcsny.org</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>https://ilchs.org/talent-recruitment</t>
+          <t>https://www.gcsny.org/ghs-clubs-activities</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Craig Young</t>
+          <t>Dillon Johnson</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>CTE:CIS and Computer Science</t>
+          <t>Robotics Club Advisor</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Inwood Early College for Health and Information Technologies, New York</t>
+          <t>Goshen Secure Center, Goshen</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>cyoung28@schools.nyc.gov</t>
+          <t>dillon.johnson@gcsny.org</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>http://www.inwoodec.org/teachers_788200</t>
+          <t>https://www.gcsny.org/ghs-clubs-activities</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Jonathan Swotinsky</t>
+          <t>Meeting Time</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Mathematics &amp; Computer Science</t>
+          <t>Computer Science Teacher</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Inwood Early College for Health and Information Technologies, New York</t>
+          <t>Goshen Secure Center, Goshen</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>jswotinsky@schools.nyc.gov</t>
+          <t>aileen.behringer@gcsny.org</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>http://www.inwoodec.org/teachers_788200</t>
+          <t>https://www.gcsny.org/ghs-clubs-activities</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Profile Photo Yvon</t>
+          <t>Alicia Gominiak</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Computer Science Teacher</t>
+          <t>Computer Science/ STEM</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>It Takes A Village Academy, Brooklyn</t>
+          <t>Gowanda High School, Gowanda</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>ymorin@schools.nyc.gov</t>
+          <t>msgominiak@gcslearn.org</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>https://www.itavabrooklyn.org/apps/staff/</t>
+          <t>https://gowcsd.org/directory/</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Ian Krywe</t>
+          <t>Peter Allen-Lamphere</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Computer Science Club Advisor</t>
+          <t>MATHEMATICS, AP COMPUTER SCIENCE, &amp; ROBOTICS</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Ithaca Senior High School, Ithaca</t>
+          <t>Gregorio Luperon High School for Science and Mathematics, New York</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>ikrywe@icsd.k12.ny.us</t>
+          <t>plamphe@schools.nyc.gov</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>https://sites.google.com/view/ithacastemadvocates/associates</t>
+          <t>https://www.glhs.nyc/staff</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Jennifer Andrews</t>
+          <t>Michael Piscitelli</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Supervisor of Math, Science &amp; Computer Science - Secondary</t>
+          <t>Computer Science Teacher</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Jackson Liberty High School, Jackson</t>
+          <t>Guilderland High School, Guilderland Center</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>jandrews@jacksonsd.org</t>
+          <t>piscitellim@guilderlandschools.net</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>https://www.jacksonsd.org/about-our-district/administrative-contacts</t>
+          <t>https://www.guilderlandschools.org/guilderland-high-school/clubs-and-activities/</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Cheryl Voelker</t>
+          <t>Kaci Nowadly</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>COMPUTER SCIENCE</t>
+          <t>Computer Club Advisor</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Jacqueline Kennedy-Onassis High School, New York</t>
+          <t>Hamburg High School, Hamburg</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>cvoelker2@schools.nyc.gov</t>
+          <t>knowadly@hcsdk12.org</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>https://img1.wsimg.com/blobby/go/36743b8c-e63e-4b88-aae9-2abcfea4f55f/2026-27%20JKO%20Table%20of%20Org%20and%20Admin%20no%20numbers.pdf</t>
+          <t>https://sites.google.com/hcsdk12.org/counselingcenter/clubs-activities-sports</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Shana Henry</t>
+          <t>Jackson Lindie</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Math/Computer Science</t>
+          <t>Computer Science Instructor</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>James Baldwin School-A School for Expeditionary Lrning, New York</t>
+          <t>Hammond Central School, Hammond</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>shenry@schools.nyc.gov</t>
+          <t>lkjackson@hammond.k12.in.us</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>https://www.thejamesbaldwinschool.org/staff-directory</t>
+          <t>https://campussuite-storage.s3.amazonaws.com/prod/1559033/fab8744a-ab41-11ea-9bfa-127f10bcdb1b/2674154/cabcb666-6222-11ee-80d6-0a58a9feac02/file/ACC%20Contact%20List%202023-24.pdf</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Andrew Erlagen</t>
+          <t>Chevonese Cornwall</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Computer Science Club Advisor</t>
+          <t>Engineering/Computer Science Teacher</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Jericho Senior High School, Jericho</t>
+          <t>Harry S Truman High School, Bronx</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>aerlagen@jerichoschools.org</t>
+          <t>ccornwall@schools.nyc.gov</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>https://www.jerichoschools.org/science-and-technology</t>
+          <t>https://www.bxtrumanhighschool.com/groups/compsci/</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Halsey Bulldog</t>
+          <t>Marisa Laks</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Computer Science Teacher</t>
+          <t>Computer Science Teacher/School Programmer</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>JHS 157 Stephen A Halsey, Rego Park</t>
+          <t>High School for Environmental Studies, New York</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>halseybulldogrobotics@halsey157.com</t>
+          <t>laks.marisa@gmail.com</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>https://halseybulldogrobot.wixsite.com/website/about-us</t>
+          <t>https://newyork.csteachers.org/cstanewyork/regions/nyc</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Cheryl Voelker</t>
+          <t>Javier Trejo</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>COMPUTER SCIENCE</t>
+          <t>Computer Science Lead</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>John F Kennedy Jr School, Elmhurst</t>
+          <t>High School for Health Careers &amp; Sciences, New York</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>cvoelker2@schools.nyc.gov</t>
+          <t>jtrejo@schools.nyc.gov</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>https://img1.wsimg.com/blobby/go/36743b8c-e63e-4b88-aae9-2abcfea4f55f/TO%20Part%20II.pdf</t>
+          <t>https://pintel.ai/school-intel/high-school-for-health-careers-and-sciences</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Jocelyn Humphries</t>
+          <t>Jeffrey Merz</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Computer Science Club Advisor</t>
+          <t>Instructor: Computer Networking &amp; Cybersecurity</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>John Jay High School, Cross River</t>
+          <t>Hunterdon County Vocational School District Central Campus, Flemington</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>jocelyn.humphries@wcsdny.orgundefined</t>
+          <t>jmerz@hcvsd.org</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>https://jjhs.wappingersschools.org/computer-science-honor-society</t>
+          <t>https://polytech.hcvsd.org/apps/pages/index.jsp?type=d&amp;uREC_ID=351129</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Paul David</t>
+          <t>Jeffrey Merz</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Computer Science Teacher</t>
+          <t>Computer Networking &amp; Cybersecurity Instructor</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>John Jay High School, Cross River</t>
+          <t>Hunterdon Polytech Bartles Corner Campus, Flemington</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>paul.david@wcsdny.org</t>
+          <t>jmerz@hcvsd.org</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>https://jjhs.wappingersschools.org/faculty</t>
+          <t>https://polytech.hcvsd.org/apps/pages/index.jsp?type=u&amp;uREC_ID=1332995</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>John Jay</t>
+          <t>Jennifer Allard</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Computer Science Club Advisor</t>
+          <t>Computer Science</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>John Jay School for Law, Brooklyn</t>
+          <t>Ichabod Crane Senior High School, Valatie</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>womencybersecurity@jjay.cuny.edu</t>
+          <t>jallard@ichabodcrane.org</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>https://www.jjay.cuny.edu/student-life/center-student-involvement-leadership/student-organizations</t>
+          <t>https://www.ichabodcrane.org/contact/</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Joel Maerten</t>
+          <t>Additional Application Instructions</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Computer Science and Cybersecurity</t>
+          <t>Computer Science Teacher</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Kenmore Junior-Senior High School, Kenmore</t>
+          <t>International Leadership Charter High School, Bronx</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>jmaerten@ktufsd.org</t>
+          <t>lbeltre@ilchs.org</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>https://www.ktufsd.org/all-departments/academic-programs-departments/engineering-technology-education</t>
+          <t>https://ilchs.org/talent-recruitment</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Devon Asboth</t>
+          <t>Craig Young</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>AP Computer Science</t>
+          <t>CTE:CIS and Computer Science</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Lake Shore Senior High School, Angola</t>
+          <t>Inwood Early College for Health and Information Technologies, New York</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>devon.asboth@lscsd.org</t>
+          <t>cyoung28@schools.nyc.gov</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>https://lshs.lakeshorecsd.org/276168_2</t>
+          <t>http://www.inwoodec.org/teachers_788200</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Robin Marrone-Mann</t>
+          <t>Jonathan Swotinsky</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>AP Computer Science</t>
+          <t>Mathematics &amp; Computer Science</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Lakeland High School, Shrub Oak</t>
+          <t>Inwood Early College for Health and Information Technologies, New York</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>rscott1@lakelandschools.org</t>
+          <t>jswotinsky@schools.nyc.gov</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>https://www.lakelandschools.org/lakelandhigh/academics/occupational_education.php</t>
+          <t>http://www.inwoodec.org/teachers_788200</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Cheryl Voelker</t>
+          <t>Profile Photo Yvon</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>COMPUTER SCIENCE</t>
+          <t>Computer Science Teacher</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Liberation Diploma Plus, Brooklyn</t>
+          <t>It Takes A Village Academy, Brooklyn</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>cvoelker2@schools.nyc.gov</t>
+          <t>ymorin@schools.nyc.gov</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>https://img1.wsimg.com/blobby/go/36743b8c-e63e-4b88-aae9-2abcfea4f55f/TO%20Part%20II.pdf</t>
+          <t>https://www.itavabrooklyn.org/apps/staff/</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Kevin Tuve</t>
+          <t>Ian Krywe</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>A.P. Computer Science</t>
+          <t>Computer Science Club Advisor</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Lodi MS HS, Lodi</t>
+          <t>Ithaca Senior High School, Ithaca</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>kevin.tuve@lodi.k12.nj.us</t>
+          <t>ikrywe@icsd.k12.ny.us</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>https://lhs.lodinjschools.org/academics/social-studies-and-business/home/teachers</t>
+          <t>https://sites.google.com/view/ithacastemadvocates/associates</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Saanvi Neema</t>
+          <t>Jennifer Andrews</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Computer Science Club Advisor</t>
+          <t>Supervisor of Math, Science &amp; Computer Science - Secondary</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Lynbrook Senior High School, Lynbrook</t>
+          <t>Jackson Liberty High School, Jackson</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>lynbrookcsclub@gmail.com</t>
+          <t>jandrews@jacksonsd.org</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>https://lynbrookcs.github.io/about/</t>
+          <t>https://www.jacksonsd.org/about-our-district/administrative-contacts</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Mx. Williamstyer</t>
+          <t>Cheryl Voelker</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Robotics Club Advisor</t>
+          <t>COMPUTER SCIENCE</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Malverne Senior High School, Malverne</t>
+          <t>Jacqueline Kennedy-Onassis High School, New York</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>rwilliamstyer@malverneschools.org</t>
+          <t>cvoelker2@schools.nyc.gov</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>https://mhs.malverneschools.org/clubs-and-activities</t>
+          <t>https://img1.wsimg.com/blobby/go/36743b8c-e63e-4b88-aae9-2abcfea4f55f/2026-27%20JKO%20Table%20of%20Org%20and%20Admin%20no%20numbers.pdf</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Jefrey Reanda</t>
+          <t>Shana Henry</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>CTE-Computer Science</t>
+          <t>Math/Computer Science</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Manhattan Bridges High School, New York</t>
+          <t>James Baldwin School-A School for Expeditionary Lrning, New York</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>jreanda@schools.nyc.gov</t>
+          <t>shenry@schools.nyc.gov</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>https://sites.google.com/manhattanbridgeshs.org/mbhs/home</t>
+          <t>https://www.thejamesbaldwinschool.org/staff-directory</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Ned Edward Lauber</t>
+          <t>Andrew Erlagen</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Geometry/ Trigonometry/ Computer Science</t>
+          <t>Computer Science Club Advisor</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Manhattan International High School, New York</t>
+          <t>Jericho Senior High School, Jericho</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>nlauber@mihsnyc.org</t>
+          <t>aerlagen@jerichoschools.org</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>https://www.mihsnyc.org/faculty</t>
+          <t>https://www.jerichoschools.org/science-and-technology</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Nelly Choueiri</t>
+          <t>Halsey Bulldog</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Algebra &amp; Computer Science</t>
+          <t>Computer Science Teacher</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Manhattan International High School, New York</t>
+          <t>JHS 157 Stephen A Halsey, Rego Park</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>nchoueiri@mihsnyc.org</t>
+          <t>halseybulldogrobotics@halsey157.com</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>https://www.mihsnyc.org/faculty</t>
+          <t>https://halseybulldogrobot.wixsite.com/website/about-us</t>
         </is>
       </c>
     </row>
@@ -2373,7 +2373,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Marie Curie High School-Nursing, Bronx</t>
+          <t>John F Kennedy Jr School, Elmhurst</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -2390,61 +2390,61 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Jiang Yuhang</t>
+          <t>Jocelyn Humphries</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>AP Computer Science Principles</t>
+          <t>Computer Science Club Advisor</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Medgar Evers College Preparatory School, Brooklyn</t>
+          <t>John Jay High School, Cross River</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>yjiang4@schools.nyc.gov</t>
+          <t>jocelyn.humphries@wcsdny.orgundefined</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>https://www.mecps.org/apps/pages/index.jsp?type=u&amp;uREC_ID=725949</t>
+          <t>https://jjhs.wappingersschools.org/computer-science-honor-society</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Maxwell Yearwood</t>
+          <t>Paul David</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>AP Computer Science A</t>
+          <t>Computer Science Teacher</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Medgar Evers College Preparatory School, Brooklyn</t>
+          <t>John Jay High School, Cross River</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>myearwo2@schools.nyc.gov</t>
+          <t>paul.david@wcsdny.org</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>https://www.mecps.org/apps/pages/index.jsp?pREC_ID=972348&amp;termREC_ID=&amp;type=d&amp;uREC_ID=498596</t>
+          <t>https://jjhs.wappingersschools.org/faculty</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Scott Gray</t>
+          <t>John Jay</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -2454,888 +2454,888 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Middleburgh Junior/Senior High School, Middleburgh</t>
+          <t>John Jay School for Law, Brooklyn</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>scott.gray@mcsdny.org</t>
+          <t>womencybersecurity@jjay.cuny.edu</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>https://www.middleburghcsd.org/clubs-class-organizations-and-extra-curricular-activities/</t>
+          <t>https://www.jjay.cuny.edu/student-life/center-student-involvement-leadership/student-organizations</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Jessica Guthrie</t>
+          <t>Paul David</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Computer Science Essentials - Computer Science Principles - Intro to Software Development - Web Design</t>
+          <t>Computer Science Teacher</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Middletown High School, Middletown</t>
+          <t>John Jay Senior High School, Hopewell Junction</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>jessica.guthrie@ecsdm.org</t>
+          <t>paul.david@wcsdny.org</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>https://sites.google.com/ecsdm.org/mhstechnology/meet-the-teachers</t>
+          <t>https://jjhs.wappingersschools.org/faculty</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Juliano DeSouza</t>
+          <t>Joel Maerten</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Cisco Systems/Cybersecurity Teacher</t>
+          <t>Computer Science and Cybersecurity</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Mount Vernon High School, Mount Vernon</t>
+          <t>Kenmore Junior-Senior High School, Kenmore</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>jalvesdesouza@mtvernoncsd.org</t>
+          <t>jmaerten@ktufsd.org</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>https://mvhs.mtvernoncsd.org/programs/career-and-technical-education/cisco-systemscybersecurity</t>
+          <t>https://www.ktufsd.org/all-departments/academic-programs-departments/engineering-technology-education</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Cheryl Voelker</t>
+          <t>Devon Asboth</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>COMPUTER SCIENCE</t>
+          <t>AP Computer Science</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>New Directions Secondary School, Bronx</t>
+          <t>Lake Shore Senior High School, Angola</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>cvoelker2@schools.nyc.gov</t>
+          <t>devon.asboth@lscsd.org</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>https://img1.wsimg.com/blobby/go/36743b8c-e63e-4b88-aae9-2abcfea4f55f/TO%20Part%20II.pdf</t>
+          <t>https://lshs.lakeshorecsd.org/276168_2</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Have You Visit</t>
+          <t>Robin Marrone-Mann</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Computer Science Teacher</t>
+          <t>AP Computer Science</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>New York State School for the Deaf, Rome</t>
+          <t>Lakeland High School, Shrub Oak</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>ask@nysd.net</t>
+          <t>rscott1@lakelandschools.org</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>https://www.nysd.net/steam-lab.html</t>
+          <t>https://www.lakelandschools.org/lakelandhigh/academics/occupational_education.php</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Lakeisha Stokes</t>
+          <t>Greg Goss</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Department Chairperson-Computer Science/CTE</t>
+          <t>Computer Science Teacher</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Newark Sch of Data Science and Information Technology, Newark</t>
+          <t>Leap Academy University Charter School, Camden</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>l1stokes@nps.k12.nj.us</t>
+          <t>ggoss@leap.rutgers.edu</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>https://www.nps.k12.nj.us/data-science/homepage/staff-members/</t>
+          <t>https://www.leapacademycharter.org/schools/high-school/</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Samantha Ames</t>
+          <t>Cheryl Voelker</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Computer Science/CTE Faculty</t>
+          <t>COMPUTER SCIENCE</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Newark Sch of Data Science and Information Technology, Newark</t>
+          <t>Liberation Diploma Plus, Brooklyn</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>sames@nps.k12.nj.us</t>
+          <t>cvoelker2@schools.nyc.gov</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>https://www.nps.k12.nj.us/data-science/homepage/staff-members/</t>
+          <t>https://img1.wsimg.com/blobby/go/36743b8c-e63e-4b88-aae9-2abcfea4f55f/TO%20Part%20II.pdf</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Ricardo Longo</t>
+          <t>Kevin Tuve</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Computer Science Lead</t>
+          <t>A.P. Computer Science</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>NYC Charter HS - Aeci, Bronx</t>
+          <t>Lodi MS HS, Lodi</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>jreynoso@aecicharterhs.org</t>
+          <t>kevin.tuve@lodi.k12.nj.us</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>https://pintel.ai/school-intel/aeci-ii-charter-high-school</t>
+          <t>https://lhs.lodinjschools.org/academics/social-studies-and-business/home/teachers</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Santiago Taveras</t>
+          <t>Saanvi Neema</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Computer Science Teacher</t>
+          <t>Computer Science Club Advisor</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>NYC Charter HS - Aeci, Bronx</t>
+          <t>Lynbrook Senior High School, Lynbrook</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>staveras@aecicharterhs.org</t>
+          <t>lynbrookcsclub@gmail.com</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>https://pintel.ai/school-intel/aeci-ii-charter-high-school</t>
+          <t>https://lynbrookcs.github.io/about/</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Nicholas Apicella</t>
+          <t>Mx. Williamstyer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Mathematics/Computer Science Teacher</t>
+          <t>Robotics Club Advisor</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Ossining High School, Ossining</t>
+          <t>Malverne Senior High School, Malverne</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>napicella@ossiningufsd.org</t>
+          <t>rwilliamstyer@malverneschools.org</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>https://amd.ossiningufsd.org/fs/elements/9833/print</t>
+          <t>https://mhs.malverneschools.org/clubs-and-activities</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Shayne Rothman</t>
+          <t>Jefrey Reanda</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Computer Science</t>
+          <t>CTE-Computer Science</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Park Slope Collegiate, Brooklyn</t>
+          <t>Manhattan Bridges High School, New York</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>srothman5@schools.nyc.gov</t>
+          <t>jreanda@schools.nyc.gov</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>https://www.parkslopecollegiate.org/about</t>
+          <t>https://sites.google.com/manhattanbridgeshs.org/mbhs/home</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Tom Callahan</t>
+          <t>Ned Edward Lauber</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Computer Science Club Advisor</t>
+          <t>Geometry/ Trigonometry/ Computer Science</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Pelham Memorial High School, Pelham</t>
+          <t>Manhattan International High School, New York</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>tcallahan@pelhamschools.org</t>
+          <t>nlauber@mihsnyc.org</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>https://pmhs.pelhamschools.org/teaching-and-learning/science-department</t>
+          <t>https://www.mihsnyc.org/faculty</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Division Sag</t>
+          <t>Nelly Choueiri</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Computer Science Club Advisor</t>
+          <t>Algebra &amp; Computer Science</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Pierson Middle/High School, Sag Harbor</t>
+          <t>Manhattan International High School, New York</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>mailbag@27east.com</t>
+          <t>nchoueiri@mihsnyc.org</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>https://www.27east.com/sag-harbor-express/news/education/article_26e2093c-4e4d-5298-9907-09ceea6f7856.html</t>
+          <t>https://www.mihsnyc.org/faculty</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Katie Livermore</t>
+          <t>Cheryl Voelker</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Computer Science Teacher</t>
+          <t>COMPUTER SCIENCE</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Poughkeepsie High School, Poughkeepsie</t>
+          <t>Marie Curie High School-Nursing, Bronx</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>klivermo@poughkeepsieschools.org</t>
+          <t>cvoelker2@schools.nyc.gov</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>https://poughkeepsiecsd5.smartsiteshost.com/overview-2</t>
+          <t>https://img1.wsimg.com/blobby/go/36743b8c-e63e-4b88-aae9-2abcfea4f55f/TO%20Part%20II.pdf</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Cheryl Voelker</t>
+          <t>Tamika Reese</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>COMPUTER SCIENCE</t>
+          <t>Computer Science Lead</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Providing Urban Learners Success in Education High School, Bronx</t>
+          <t>Marion P. Thomas Charter School, Newark</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>cvoelker2@schools.nyc.gov</t>
+          <t>treese@mptcs.org</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>https://img1.wsimg.com/blobby/go/36743b8c-e63e-4b88-aae9-2abcfea4f55f/TO%20Part%20II.pdf</t>
+          <t>https://www.mptcs.org/academics-orteaching-learning/scienceinnovation</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Meghan Parenteau</t>
+          <t>Jiang Yuhang</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Computer Science Teacher</t>
+          <t>AP Computer Science Principles</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>PS 256, Syosset</t>
+          <t>Medgar Evers College Preparatory School, Brooklyn</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>mparenteau@syossetschools.org</t>
+          <t>yjiang4@schools.nyc.gov</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>https://shs.syossetschools.org/departments-31f99405-c615-42ef-88f6-d52b5edff15c/computer-science</t>
+          <t>https://www.mecps.org/apps/pages/index.jsp?type=u&amp;uREC_ID=725949</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Seung Chung-Glus</t>
+          <t>Maxwell Yearwood</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Computer Science/STEM</t>
+          <t>AP Computer Science A</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>PS 94, New York</t>
+          <t>Medgar Evers College Preparatory School, Brooklyn</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>schungglus@schools.nyc.gov</t>
+          <t>myearwo2@schools.nyc.gov</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>https://sites.google.com/schools.nyc.gov/ps94qdavidporterschool/about-us/staff</t>
+          <t>https://www.mecps.org/apps/pages/index.jsp?pREC_ID=972348&amp;termREC_ID=&amp;type=d&amp;uREC_ID=498596</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Event Rachelle</t>
+          <t>Scott Gray</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Computer Science Lead</t>
+          <t>Computer Science Club Advisor</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Quest to Learn, New York</t>
+          <t>Middleburgh Junior/Senior High School, Middleburgh</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>rgontee@schools.nyc.gov</t>
+          <t>scott.gray@mcsdny.org</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>https://q2l.org/programs-partnerships/</t>
+          <t>https://www.middleburghcsd.org/clubs-class-organizations-and-extra-curricular-activities/</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Game Design</t>
+          <t>Jessica Guthrie</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Computer Science Teacher</t>
+          <t>Computer Science Essentials - Computer Science Principles - Intro to Software Development - Web Design</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Ralph R McKee Career and Technical Education High School, Staten Island</t>
+          <t>Middletown High School, Middletown</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>jpecora5@schools.nyc.gov</t>
+          <t>jessica.guthrie@ecsdm.org</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>https://mckeecths.org/apps/pages/index.jsp?type=d&amp;uREC_ID=622298</t>
+          <t>https://sites.google.com/ecsdm.org/mhstechnology/meet-the-teachers</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Martin Medina</t>
+          <t>Privacy Policy</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Computer Science</t>
+          <t>Computer Science Teacher</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Renaissance Charter School, Jackson Heights</t>
+          <t>Monroe 1 BOCES, Fairport</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>martinmedina@rencharter.org</t>
+          <t>monroeone_webmaster@boces.monroe.edu</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>https://rencharters.org/trcs-jackson-heights/staff-directory/</t>
+          <t>https://ny02216770.schoolwires.net/Page/6558</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Martin Medina</t>
+          <t>Brian Young</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Computer Science</t>
+          <t>Computer Science Club Advisor</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Renaissance Charter School 2 (the), Elmhurst</t>
+          <t>Morris Co Jdc, Morristown</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>martinmedina@rencharter.org</t>
+          <t>brian.young@msdk12.net</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>https://rencharters.org/trcs-jackson-heights/staff-directory/</t>
+          <t>https://mhs.morrisschooldistrict.org/academics/stem-academy-at-mhs</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Robert Dilworth</t>
+          <t>Carina Navarro</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Computer Science</t>
+          <t>Supervisor of Computer Science</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Riverhead Senior High School, Riverhead</t>
+          <t>Morris Co Jdc, Morristown</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>robert.dilworthjr@g.riverhead.net</t>
+          <t>carina.navarro@msdk12.net</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>https://www.riverhead.net/wp-content/uploads/2022/10/High-School-Achievement-Academy.pdf</t>
+          <t>https://mhs.morrisschooldistrict.org/about-us/admin-team</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Google Meets Link</t>
+          <t>Brian Young</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Computer Science Teacher</t>
+          <t>Computer Science Club Advisor</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Rockaway Park High School for Environmental Sustainability, Rockaway Park</t>
+          <t>Morris Regional School, Morristown</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>ebickard@schools.nyc.gov</t>
+          <t>brian.young@msdk12.net</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>https://rockawayparkhighschool.net/event/virtual-parent-teacher-conference-links/</t>
+          <t>https://mhs.morrisschooldistrict.org/academics/stem-academy-at-mhs</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Annmarie Amico</t>
+          <t>Carina Navarro</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Computer Science</t>
+          <t>Supervisor of Computer Science</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Roslyn Heights Elementary School, Roslyn Heights</t>
+          <t>Morris Regional School, Morristown</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>aamico@roslynschools.org</t>
+          <t>carina.navarro@msdk12.net</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>https://eh.roslynschools.org/about-our-school/contact-us</t>
+          <t>https://mhs.morrisschooldistrict.org/about-us/admin-team</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Joelle Henry</t>
+          <t>Juliano DeSouza</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Computer Science &amp; Technology</t>
+          <t>Cisco Systems/Cybersecurity Teacher</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Salem High School, Salem</t>
+          <t>Mount Vernon High School, Mount Vernon</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>joelle.henry@sau57.org</t>
+          <t>jalvesdesouza@mtvernoncsd.org</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>https://sau57.org/cte-directory</t>
+          <t>https://mvhs.mtvernoncsd.org/programs/career-and-technical-education/cisco-systemscybersecurity</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Mosaic Maniacs</t>
+          <t>David Wang</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Computer Science Club Advisor</t>
+          <t>Computer Science Coordinator</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Scarsdale Middle School, Scarsdale</t>
+          <t>N. A. Bleshman Regional Day School, Paramus</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>mfreedman-carmen@scarsdaleschools.org</t>
+          <t>dwang@bergen.edu</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>https://sms.scarsdaleschools.org/78779_3</t>
+          <t>https://bergen.edu/csit/</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Web Development</t>
+          <t>Mark Balzarette</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Computer Science Teacher</t>
+          <t>Computer Science &amp; Information Technology Department Chair</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>School for Human Rights (the), Brooklyn</t>
+          <t>N. A. Bleshman Regional Day School, Paramus</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>teals@seidohl.com</t>
+          <t>mbalzarette@bergen.edu</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>https://teals-test.neocities.org/</t>
+          <t>https://bergen.edu/csit/</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Jonathan Ryan</t>
+          <t>Cheryl Voelker</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Computer Science Club Advisor</t>
+          <t>COMPUTER SCIENCE</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Sherburne-Earlville Senior High School, Sherburne</t>
+          <t>New Directions Secondary School, Bronx</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>ryanj@seonline.org</t>
+          <t>cvoelker2@schools.nyc.gov</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>https://www.secsd.org/Robotics.aspx</t>
+          <t>https://img1.wsimg.com/blobby/go/36743b8c-e63e-4b88-aae9-2abcfea4f55f/TO%20Part%20II.pdf</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Jack McCoy</t>
+          <t>David Szeto</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Math/AP Computer Science</t>
+          <t>CTE- Computer Science</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>South Bronx Preparatory - A College Board School, Bronx</t>
+          <t>New Jersey Training School, Jamesburg</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>jmccoy2@schools.nyc.gov</t>
+          <t>dszeto@nps.k12.nj.us</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>https://www.southbronxprep.net/12th_grade</t>
+          <t>https://www.nps.k12.nj.us/tec/school-staff/faculty/</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Jarius Toogood</t>
+          <t>Have You Visit</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Robotics</t>
+          <t>Computer Science Teacher</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>South Bronx Preparatory - A College Board School, Bronx</t>
+          <t>New York State School for the Deaf, Rome</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>jtoogood@schools.nyc.gov</t>
+          <t>ask@nysd.net</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>https://www.southbronxprep.net/12th_grade</t>
+          <t>https://www.nysd.net/steam-lab.html</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Meghan Parenteau</t>
+          <t>Lakeisha Stokes</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Computer Science Teacher</t>
+          <t>Department Chairperson-Computer Science/CTE</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Syosset Senior High School, Syosset</t>
+          <t>Newark Sch of Data Science and Information Technology, Newark</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>mparenteau@syossetschools.org</t>
+          <t>l1stokes@nps.k12.nj.us</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>https://shs.syossetschools.org/departments-31f99405-c615-42ef-88f6-d52b5edff15c/computer-science</t>
+          <t>https://www.nps.k12.nj.us/data-science/homepage/staff-members/</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Dawn Trebour</t>
+          <t>Samantha Ames</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Computer Science Club Advisor</t>
+          <t>Computer Science/CTE Faculty</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Thomas A Edison Career and Technical Education High School, Jamaica</t>
+          <t>Newark Sch of Data Science and Information Technology, Newark</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>dtrebour@schools.nyc.gov</t>
+          <t>sames@nps.k12.nj.us</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>https://www.taehs.org/school-counselors</t>
+          <t>https://www.nps.k12.nj.us/data-science/homepage/staff-members/</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Edward Wang</t>
+          <t>Ricardo Longo</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>High School Science Computer Science</t>
+          <t>Computer Science Lead</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Thurgood Marshall Academy for Learning &amp; Social Change, New York</t>
+          <t>NYC Charter HS - Aeci, Bronx</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>ewang100@schools.nyc.gov</t>
+          <t>jreynoso@aecicharterhs.org</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>https://www.tmanyc.org/contact-us/science-department</t>
+          <t>https://pintel.ai/school-intel/aeci-ii-charter-high-school</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Hadley Lindsey</t>
+          <t>Santiago Taveras</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -3345,312 +3345,1230 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>University Preparatory Charter School for Young Men, Rochester</t>
+          <t>NYC Charter HS - Aeci, Bronx</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>lindsey.hadley@uprep.org</t>
+          <t>staveras@aecicharterhs.org</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>https://img1.wsimg.com/blobby/go/97d9ba3f-d7b7-48da-98f7-42f53aea0155/downloads/9th%20Grade%20Online%20Contacts%20and%20Zoom%20Times.pdf?ver=1605650909245</t>
+          <t>https://pintel.ai/school-intel/aeci-ii-charter-high-school</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>James Quinn</t>
+          <t>Lesley Potts-Langdon</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Teacher (Computer Science)</t>
+          <t>Computer Science</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Urban Assembly School for Applied Math and Science (the), Bronx</t>
+          <t>Ocean Co Jdc, Toms River</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>jquinn@amsbronx.org</t>
+          <t>lpotts-langdon@ocvts.org</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>https://www.amsbronx.org/staff-emails</t>
+          <t>https://sites.google.com/ocvts.org/trcenter/contact-information</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Thomas Feola</t>
+          <t>Nicholas Apicella</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Elementary Computer Science Technology Teacher Leader</t>
+          <t>Mathematics/Computer Science Teacher</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Vernon-Verona-Sherrill Senior High School, Verona</t>
+          <t>Ossining High School, Ossining</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>tfeola@vvsschools.org</t>
+          <t>napicella@ossiningufsd.org</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>https://www.vvsschools.org/departments/technology-services</t>
+          <t>https://amd.ossiningufsd.org/fs/elements/9833/print</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Tiffany Mack</t>
+          <t>Kelli Grab</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Computer Science Club Advisor</t>
+          <t>CTE Content Computer Science Trade and Technical</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Washington Heights Expeditionary Learning School, New York</t>
+          <t>Otsego-Delaware-Schoharie-Greene BOCES, Grand Gorge</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>tmack@schools.nyc.gov</t>
+          <t>kelli.grab@nysed.gov</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>https://wheels.echalksites.com/extracurriculars</t>
+          <t>https://www.acteonline.org/wp-content/uploads/2024/01/ACTEA-Directory-2024.pdf</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Jacquelyn Prince</t>
+          <t>Shayne Rothman</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Computer Science/Intro to Business</t>
+          <t>Computer Science</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Waverly High School, Waverly</t>
+          <t>Park Slope Collegiate, Brooklyn</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>princej@hcss.org</t>
+          <t>srothman5@schools.nyc.gov</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>https://wchs.hcss.org/faculty</t>
+          <t>https://www.parkslopecollegiate.org/about</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Chandan Sarkar</t>
+          <t>Alizah Memon</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>computer science teacher</t>
+          <t>Computer Science Teacher</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Westhill High School, Syracuse</t>
+          <t>Paterson Arts and Science Charter School, Paterson</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>csarkar@stamfordct.gov</t>
+          <t>alizah.memon@pcsst.org</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>https://www.westhillcs.com/contact</t>
+          <t>https://www.pcsst.org/8-12/departments/science/</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Rajinder Kazanchi</t>
+          <t>Alizah Memon</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Robotics teacher</t>
+          <t>Computer Science Teacher</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Westhill High School, Syracuse</t>
+          <t>Paterson Charter School for Science and Technology, Paterson</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>rkumar@stamfordct.gov</t>
+          <t>alizah.memon@pcsst.org</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>https://www.westhillcs.com/contact</t>
+          <t>https://www.pcsst.org/8-12/departments/science/</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Stock Market</t>
+          <t>Tom Callahan</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Computer Science Teacher</t>
+          <t>Computer Science Club Advisor</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Westhill High School, Syracuse</t>
+          <t>Pelham Memorial High School, Pelham</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>jesker@stamfordct.gov</t>
+          <t>tcallahan@pelhamschools.org</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>https://www.westhillcs.com/contact</t>
+          <t>https://pmhs.pelhamschools.org/teaching-and-learning/science-department</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Tarah Montalbano</t>
+          <t>Division Sag</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Computer Science Teacher</t>
+          <t>Computer Science Club Advisor</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>William E Grady Career and Technical Education High School, Brooklyn</t>
+          <t>Pierson Middle/High School, Sag Harbor</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>tmontalbano@schools.nyc.gov</t>
+          <t>mailbag@27east.com</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>https://gradyhs.com/</t>
+          <t>https://www.27east.com/sag-harbor-express/news/education/article_26e2093c-4e4d-5298-9907-09ceea6f7856.html</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Linda Perry</t>
+          <t>Katie Livermore</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Computer Science Lead</t>
+          <t>Computer Science Teacher</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>York Early College Academy, Jamaica</t>
+          <t>Poughkeepsie High School, Poughkeepsie</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>lperry5@schools.nyc.gov</t>
+          <t>klivermo@poughkeepsieschools.org</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>https://cecd28.org/SY2526/NOVEMBER/York%20Early%20College%20Academy%20(2).pdf</t>
+          <t>https://poughkeepsiecsd5.smartsiteshost.com/overview-2</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Andreas Andy Jordan</t>
+          <t>Cheryl Voelker</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Computer Science Teacher</t>
+          <t>COMPUTER SCIENCE</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Young Women's Leadership School, New York</t>
+          <t>Providing Urban Learners Success in Education High School, Bronx</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>ajordan17@schools.nyc.gov</t>
+          <t>cvoelker2@schools.nyc.gov</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>https://www.tywls-astoria.org/apps/staff</t>
+          <t>https://img1.wsimg.com/blobby/go/36743b8c-e63e-4b88-aae9-2abcfea4f55f/TO%20Part%20II.pdf</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
+          <t>Meghan Parenteau</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Computer Science Teacher</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>PS 256, Syosset</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>mparenteau@syossetschools.org</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>https://shs.syossetschools.org/departments-31f99405-c615-42ef-88f6-d52b5edff15c/computer-science</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Seung Chung-Glus</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Computer Science/STEM</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>PS 94, New York</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>schungglus@schools.nyc.gov</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>https://sites.google.com/schools.nyc.gov/ps94qdavidporterschool/about-us/staff</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Event Rachelle</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Computer Science Lead</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Quest to Learn, New York</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>rgontee@schools.nyc.gov</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>https://q2l.org/programs-partnerships/</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Game Design</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Computer Science Teacher</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Ralph R McKee Career and Technical Education High School, Staten Island</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>jpecora5@schools.nyc.gov</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>https://mckeecths.org/apps/pages/index.jsp?type=d&amp;uREC_ID=622298</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Martin Medina</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Computer Science</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Renaissance Charter School, Jackson Heights</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>martinmedina@rencharter.org</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>https://rencharters.org/trcs-jackson-heights/staff-directory/</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Martin Medina</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Computer Science</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Renaissance Charter School 2 (the), Elmhurst</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>martinmedina@rencharter.org</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>https://rencharters.org/trcs-jackson-heights/staff-directory/</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Robert Dilworth</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Computer Science</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Riverhead Senior High School, Riverhead</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>robert.dilworthjr@g.riverhead.net</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>https://www.riverhead.net/wp-content/uploads/2022/10/High-School-Achievement-Academy.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Deniz Yaman</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Computer Science Club Advisor</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Rochester Academy of Science Charter School, Rochester</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>yaman@rocsci.org</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>https://sites.google.com/buffsci.org/rocscihigh/home</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Google Meets Link</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Computer Science Teacher</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Rockaway Park High School for Environmental Sustainability, Rockaway Park</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>ebickard@schools.nyc.gov</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>https://rockawayparkhighschool.net/event/virtual-parent-teacher-conference-links/</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Annmarie Amico</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Computer Science</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Roslyn Heights Elementary School, Roslyn Heights</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>aamico@roslynschools.org</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>https://eh.roslynschools.org/about-our-school/contact-us</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Joelle Henry</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Computer Science &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Salem High School, Salem</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>joelle.henry@sau57.org</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>https://sau57.org/cte-directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Mosaic Maniacs</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Computer Science Club Advisor</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Scarsdale Middle School, Scarsdale</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>mfreedman-carmen@scarsdaleschools.org</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>https://sms.scarsdaleschools.org/78779_3</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Web Development</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Computer Science Teacher</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>School for Human Rights (the), Brooklyn</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>teals@seidohl.com</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>https://teals-test.neocities.org/</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Jonathan Ryan</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Computer Science Club Advisor</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Sherburne-Earlville Senior High School, Sherburne</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>ryanj@seonline.org</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>https://www.secsd.org/Robotics.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Jack McCoy</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Math/AP Computer Science</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>South Bronx Preparatory - A College Board School, Bronx</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>jmccoy2@schools.nyc.gov</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>https://www.southbronxprep.net/12th_grade</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Jarius Toogood</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Robotics</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>South Bronx Preparatory - A College Board School, Bronx</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>jtoogood@schools.nyc.gov</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>https://www.southbronxprep.net/12th_grade</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Susan Zieres Teeple</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Cyber Security &amp; Technology Contract Consortium Coordinator</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Sullivan BOCES, Liberty</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>susan.zieres@scboces.org</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>https://www.scboces.org/instr-support/learning-technology-cyber-security</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Meghan Parenteau</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Computer Science Teacher</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Syosset Senior High School, Syosset</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>mparenteau@syossetschools.org</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>https://shs.syossetschools.org/departments-31f99405-c615-42ef-88f6-d52b5edff15c/computer-science</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Dawn Trebour</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Computer Science Club Advisor</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Thomas A Edison Career and Technical Education High School, Jamaica</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>dtrebour@schools.nyc.gov</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>https://www.taehs.org/school-counselors</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Edward Wang</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>High School Science Computer Science</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Thurgood Marshall Academy for Learning &amp; Social Change, New York</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>ewang100@schools.nyc.gov</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>https://www.tmanyc.org/contact-us/science-department</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Hadley Lindsey</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Computer Science Teacher</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>University Preparatory Charter School for Young Men, Rochester</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>lindsey.hadley@uprep.org</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>https://img1.wsimg.com/blobby/go/97d9ba3f-d7b7-48da-98f7-42f53aea0155/downloads/9th%20Grade%20Online%20Contacts%20and%20Zoom%20Times.pdf?ver=1605650909245</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>James Quinn</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Teacher (Computer Science)</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Urban Assembly School for Applied Math and Science (the), Bronx</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>jquinn@amsbronx.org</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>https://www.amsbronx.org/staff-emails</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Amy Fox</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Computer Science Teacher</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Valhalla High School, Valhalla</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>afox@valhallaschools.org</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>https://vhs.valhallaschools.org/apps/pages/index.jsp?pREC_ID=contact&amp;type=u&amp;uREC_ID=625103</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Thomas Feola</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Elementary Computer Science Technology Teacher Leader</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Vernon-Verona-Sherrill Senior High School, Verona</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>tfeola@vvsschools.org</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>https://www.vvsschools.org/departments/technology-services</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Tiffany Mack</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Computer Science Club Advisor</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Washington Heights Expeditionary Learning School, New York</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>tmack@schools.nyc.gov</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>https://wheels.echalksites.com/extracurriculars</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Jacquelyn Prince</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Computer Science/Intro to Business</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Waverly High School, Waverly</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>princej@hcss.org</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>https://wchs.hcss.org/faculty</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Chandan Sarkar</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>computer science teacher</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Westhill High School, Syracuse</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>csarkar@stamfordct.gov</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>https://www.westhillcs.com/contact</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Rajinder Kazanchi</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Robotics teacher</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Westhill High School, Syracuse</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>rkumar@stamfordct.gov</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>https://www.westhillcs.com/contact</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Stock Market</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Computer Science Teacher</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Westhill High School, Syracuse</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>jesker@stamfordct.gov</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>https://www.westhillcs.com/contact</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Tarah Montalbano</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Computer Science Teacher</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>William E Grady Career and Technical Education High School, Brooklyn</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>tmontalbano@schools.nyc.gov</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>https://gradyhs.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Karen Greco</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Mathematics / Computer Science Director</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Williamsville East High School, East Amherst</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>kgreco@williamsvillek12.org</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>https://www.williamsvillek12.org/departments/instruction</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Christopher McGinley</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Mathematics / Computer Science Director</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Williamsville South High School, Williamsville</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>kgreco@williamsvillek12.org</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>https://www.williamsvillek12.org/departments/instruction</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Linda Perry</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Computer Science Lead</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>York Early College Academy, Jamaica</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>lperry5@schools.nyc.gov</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>https://cecd28.org/SY2526/NOVEMBER/York%20Early%20College%20Academy%20(2).pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
           <t>Andreas Andy Jordan</t>
         </is>
       </c>
-      <c r="B135" t="inlineStr">
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Computer Science Teacher</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Young Women's Leadership School, New York</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>ajordan17@schools.nyc.gov</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>https://www.tywls-astoria.org/apps/staff</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Andreas Andy Jordan</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
         <is>
           <t>AP Computer Science A</t>
         </is>
       </c>
-      <c r="C135" t="inlineStr">
+      <c r="C169" t="inlineStr">
         <is>
           <t>Young Womens Leadership School - Astoria, Long Island City</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr">
+      <c r="D169" t="inlineStr">
         <is>
           <t>andy@tywls-astoria.org</t>
         </is>
       </c>
-      <c r="E135" t="inlineStr">
+      <c r="E169" t="inlineStr">
         <is>
           <t>https://tywls-astoria.edlioschool.com/apps/pages/index.jsp?pREC_ID=1780964&amp;type=d&amp;uREC_ID=1638858</t>
         </is>
@@ -4060,6 +4978,108 @@
     <hyperlink ref="C135" r:id="rId400"/>
     <hyperlink ref="D135" r:id="rId401"/>
     <hyperlink ref="E135" r:id="rId402"/>
+    <hyperlink ref="C136" r:id="rId403"/>
+    <hyperlink ref="D136" r:id="rId404"/>
+    <hyperlink ref="E136" r:id="rId405"/>
+    <hyperlink ref="C137" r:id="rId406"/>
+    <hyperlink ref="D137" r:id="rId407"/>
+    <hyperlink ref="E137" r:id="rId408"/>
+    <hyperlink ref="C138" r:id="rId409"/>
+    <hyperlink ref="D138" r:id="rId410"/>
+    <hyperlink ref="E138" r:id="rId411"/>
+    <hyperlink ref="C139" r:id="rId412"/>
+    <hyperlink ref="D139" r:id="rId413"/>
+    <hyperlink ref="E139" r:id="rId414"/>
+    <hyperlink ref="C140" r:id="rId415"/>
+    <hyperlink ref="D140" r:id="rId416"/>
+    <hyperlink ref="E140" r:id="rId417"/>
+    <hyperlink ref="C141" r:id="rId418"/>
+    <hyperlink ref="D141" r:id="rId419"/>
+    <hyperlink ref="E141" r:id="rId420"/>
+    <hyperlink ref="C142" r:id="rId421"/>
+    <hyperlink ref="D142" r:id="rId422"/>
+    <hyperlink ref="E142" r:id="rId423"/>
+    <hyperlink ref="C143" r:id="rId424"/>
+    <hyperlink ref="D143" r:id="rId425"/>
+    <hyperlink ref="E143" r:id="rId426"/>
+    <hyperlink ref="C144" r:id="rId427"/>
+    <hyperlink ref="D144" r:id="rId428"/>
+    <hyperlink ref="E144" r:id="rId429"/>
+    <hyperlink ref="C145" r:id="rId430"/>
+    <hyperlink ref="D145" r:id="rId431"/>
+    <hyperlink ref="E145" r:id="rId432"/>
+    <hyperlink ref="C146" r:id="rId433"/>
+    <hyperlink ref="D146" r:id="rId434"/>
+    <hyperlink ref="E146" r:id="rId435"/>
+    <hyperlink ref="C147" r:id="rId436"/>
+    <hyperlink ref="D147" r:id="rId437"/>
+    <hyperlink ref="E147" r:id="rId438"/>
+    <hyperlink ref="C148" r:id="rId439"/>
+    <hyperlink ref="D148" r:id="rId440"/>
+    <hyperlink ref="E148" r:id="rId441"/>
+    <hyperlink ref="C149" r:id="rId442"/>
+    <hyperlink ref="D149" r:id="rId443"/>
+    <hyperlink ref="E149" r:id="rId444"/>
+    <hyperlink ref="C150" r:id="rId445"/>
+    <hyperlink ref="D150" r:id="rId446"/>
+    <hyperlink ref="E150" r:id="rId447"/>
+    <hyperlink ref="C151" r:id="rId448"/>
+    <hyperlink ref="D151" r:id="rId449"/>
+    <hyperlink ref="E151" r:id="rId450"/>
+    <hyperlink ref="C152" r:id="rId451"/>
+    <hyperlink ref="D152" r:id="rId452"/>
+    <hyperlink ref="E152" r:id="rId453"/>
+    <hyperlink ref="C153" r:id="rId454"/>
+    <hyperlink ref="D153" r:id="rId455"/>
+    <hyperlink ref="E153" r:id="rId456"/>
+    <hyperlink ref="C154" r:id="rId457"/>
+    <hyperlink ref="D154" r:id="rId458"/>
+    <hyperlink ref="E154" r:id="rId459"/>
+    <hyperlink ref="C155" r:id="rId460"/>
+    <hyperlink ref="D155" r:id="rId461"/>
+    <hyperlink ref="E155" r:id="rId462"/>
+    <hyperlink ref="C156" r:id="rId463"/>
+    <hyperlink ref="D156" r:id="rId464"/>
+    <hyperlink ref="E156" r:id="rId465"/>
+    <hyperlink ref="C157" r:id="rId466"/>
+    <hyperlink ref="D157" r:id="rId467"/>
+    <hyperlink ref="E157" r:id="rId468"/>
+    <hyperlink ref="C158" r:id="rId469"/>
+    <hyperlink ref="D158" r:id="rId470"/>
+    <hyperlink ref="E158" r:id="rId471"/>
+    <hyperlink ref="C159" r:id="rId472"/>
+    <hyperlink ref="D159" r:id="rId473"/>
+    <hyperlink ref="E159" r:id="rId474"/>
+    <hyperlink ref="C160" r:id="rId475"/>
+    <hyperlink ref="D160" r:id="rId476"/>
+    <hyperlink ref="E160" r:id="rId477"/>
+    <hyperlink ref="C161" r:id="rId478"/>
+    <hyperlink ref="D161" r:id="rId479"/>
+    <hyperlink ref="E161" r:id="rId480"/>
+    <hyperlink ref="C162" r:id="rId481"/>
+    <hyperlink ref="D162" r:id="rId482"/>
+    <hyperlink ref="E162" r:id="rId483"/>
+    <hyperlink ref="C163" r:id="rId484"/>
+    <hyperlink ref="D163" r:id="rId485"/>
+    <hyperlink ref="E163" r:id="rId486"/>
+    <hyperlink ref="C164" r:id="rId487"/>
+    <hyperlink ref="D164" r:id="rId488"/>
+    <hyperlink ref="E164" r:id="rId489"/>
+    <hyperlink ref="C165" r:id="rId490"/>
+    <hyperlink ref="D165" r:id="rId491"/>
+    <hyperlink ref="E165" r:id="rId492"/>
+    <hyperlink ref="C166" r:id="rId493"/>
+    <hyperlink ref="D166" r:id="rId494"/>
+    <hyperlink ref="E166" r:id="rId495"/>
+    <hyperlink ref="C167" r:id="rId496"/>
+    <hyperlink ref="D167" r:id="rId497"/>
+    <hyperlink ref="E167" r:id="rId498"/>
+    <hyperlink ref="C168" r:id="rId499"/>
+    <hyperlink ref="D168" r:id="rId500"/>
+    <hyperlink ref="E168" r:id="rId501"/>
+    <hyperlink ref="C169" r:id="rId502"/>
+    <hyperlink ref="D169" r:id="rId503"/>
+    <hyperlink ref="E169" r:id="rId504"/>
   </hyperlinks>
 </worksheet>
 </file>